--- a/knowledge_base/source/06_evidence_mapping.xlsx
+++ b/knowledge_base/source/06_evidence_mapping.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_evidence_mapping" sheetId="1" r:id="R190c4823309a4507"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_evidence_mapping" sheetId="1" r:id="R39335f8872d34cab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2002,7 +2002,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F60" s="32" t="str">
-        <x:v>TP-153 is uploaded</x:v>
+        <x:v>TP-153 CLO section is present or expected</x:v>
       </x:c>
       <x:c r="G60" s="32" t="str">
         <x:v>Not Verified</x:v>
@@ -2054,7 +2054,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F62" s="32" t="str">
-        <x:v>TP-153 is uploaded</x:v>
+        <x:v>TP-153 topic section is present or expected</x:v>
       </x:c>
       <x:c r="G62" s="32" t="str">
         <x:v>Not Verified</x:v>
@@ -2106,7 +2106,7 @@
         <x:v>Conditional</x:v>
       </x:c>
       <x:c r="F64" s="32" t="str">
-        <x:v>Assessment-method comparison is requested</x:v>
+        <x:v>Assessment-method comparison is part of the mandatory analysis</x:v>
       </x:c>
       <x:c r="G64" s="32" t="str">
         <x:v>Not Verified</x:v>
@@ -2132,7 +2132,7 @@
         <x:v>Conditional</x:v>
       </x:c>
       <x:c r="F65" s="32" t="str">
-        <x:v>Assessment-activity comparison is requested</x:v>
+        <x:v>Assessment-activity comparison is part of the mandatory analysis</x:v>
       </x:c>
       <x:c r="G65" s="32" t="str">
         <x:v>Not Verified</x:v>
@@ -2326,7 +2326,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9f3be9d7e1b4350"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac5ab72b17824e00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/knowledge_base/source/06_evidence_mapping.xlsx
+++ b/knowledge_base/source/06_evidence_mapping.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_evidence_mapping" sheetId="1" r:id="R39335f8872d34cab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_evidence_mapping" sheetId="1" r:id="R91fdc93b8dfa4cea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -166,7 +166,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="42">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -269,6 +269,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1202,7 +1203,7 @@
         <x:v>Not Verified</x:v>
       </x:c>
       <x:c r="H29" s="38" t="str">
-        <x:v>Used to evaluate task clarity.</x:v>
+        <x:v>Used only to evaluate whether the action and expected response are recognizable.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="42" customHeight="1">
@@ -1228,7 +1229,7 @@
         <x:v>Not Verified</x:v>
       </x:c>
       <x:c r="H30" s="38" t="str">
-        <x:v>Used to evaluate ambiguity and contradiction.</x:v>
+        <x:v>Used only to evaluate linguistic ambiguity, contradiction, and unclear terminology.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="42" customHeight="1">
@@ -1242,19 +1243,19 @@
         <x:v>EV002</x:v>
       </x:c>
       <x:c r="D31" s="32" t="str">
-        <x:v>Question text and context</x:v>
+        <x:v>Question text and confirmed question-specific context</x:v>
       </x:c>
       <x:c r="E31" s="32" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F31" s="32" t="str">
-        <x:v>Question and surrounding context are readable</x:v>
+        <x:v>Question text is readable</x:v>
       </x:c>
       <x:c r="G31" s="32" t="str">
         <x:v>Not Verified</x:v>
       </x:c>
       <x:c r="H31" s="38" t="str">
-        <x:v>Used to verify information completeness.</x:v>
+        <x:v>Used to verify completeness together with confirmed supporting context.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="42" customHeight="1">
@@ -1274,13 +1275,13 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="F32" s="32" t="str">
-        <x:v>Question contains separate instructions</x:v>
+        <x:v>The question contains separate question-specific instructions</x:v>
       </x:c>
       <x:c r="G32" s="32" t="str">
         <x:v>Not Verified</x:v>
       </x:c>
       <x:c r="H32" s="38" t="str">
-        <x:v>Supporting evidence for completeness.</x:v>
+        <x:v>Optional context for question completeness; it is excluded from the exam-level instructions rule.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="42" customHeight="1">
@@ -1762,19 +1763,19 @@
         <x:v>EV006</x:v>
       </x:c>
       <x:c r="D51" s="32" t="str">
-        <x:v>General instructions</x:v>
+        <x:v>Exam-level general instructions</x:v>
       </x:c>
       <x:c r="E51" s="32" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Conditional</x:v>
       </x:c>
       <x:c r="F51" s="32" t="str">
-        <x:v>General instruction area is readable</x:v>
+        <x:v>Exam-level general instructions are present or required</x:v>
       </x:c>
       <x:c r="G51" s="32" t="str">
         <x:v>Not Verified</x:v>
       </x:c>
       <x:c r="H51" s="38" t="str">
-        <x:v>Used to check exam-level instructions.</x:v>
+        <x:v>Used only for general answer requirements, resources or tools, constraints, and submission or formatting directions.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="42" customHeight="1">
@@ -1785,22 +1786,22 @@
         <x:v>REQ021</x:v>
       </x:c>
       <x:c r="C52" s="32" t="str">
-        <x:v>EV007</x:v>
+        <x:v>EV001</x:v>
       </x:c>
       <x:c r="D52" s="32" t="str">
-        <x:v>Question-specific instructions</x:v>
+        <x:v>Exam-level evaluation anchor</x:v>
       </x:c>
       <x:c r="E52" s="32" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="F52" s="32" t="str">
-        <x:v>Questions require special instructions</x:v>
+        <x:v>RULE021 is executed</x:v>
       </x:c>
       <x:c r="G52" s="32" t="str">
         <x:v>Not Verified</x:v>
       </x:c>
       <x:c r="H52" s="38" t="str">
-        <x:v>Used when applicable.</x:v>
+        <x:v>Provides the exam-level source record; question-specific instructions and supporting-material availability are excluded from this rule.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="42" customHeight="1">
@@ -2323,10 +2324,88 @@
         <x:v>Explanation must point to traceable evidence.</x:v>
       </x:c>
     </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="30" t="str">
+        <x:v>MAP072</x:v>
+      </x:c>
+      <x:c r="B73" s="30" t="str">
+        <x:v>REQ013</x:v>
+      </x:c>
+      <x:c r="C73" s="30" t="str">
+        <x:v>EV008</x:v>
+      </x:c>
+      <x:c r="D73" s="30" t="str">
+        <x:v>Confirmed figure or diagram context</x:v>
+      </x:c>
+      <x:c r="E73" s="30" t="str">
+        <x:v>Conditional</x:v>
+      </x:c>
+      <x:c r="F73" s="30" t="str">
+        <x:v>The question refers to or depends on a figure or diagram</x:v>
+      </x:c>
+      <x:c r="G73" s="30" t="str">
+        <x:v>Not Verified</x:v>
+      </x:c>
+      <x:c r="H73" s="30" t="str">
+        <x:v>Included as question-specific context when confirmed and associated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="30" t="str">
+        <x:v>MAP073</x:v>
+      </x:c>
+      <x:c r="B74" s="30" t="str">
+        <x:v>REQ013</x:v>
+      </x:c>
+      <x:c r="C74" s="30" t="str">
+        <x:v>EV009</x:v>
+      </x:c>
+      <x:c r="D74" s="30" t="str">
+        <x:v>Confirmed table context</x:v>
+      </x:c>
+      <x:c r="E74" s="30" t="str">
+        <x:v>Conditional</x:v>
+      </x:c>
+      <x:c r="F74" s="30" t="str">
+        <x:v>The question refers to or depends on a table</x:v>
+      </x:c>
+      <x:c r="G74" s="30" t="str">
+        <x:v>Not Verified</x:v>
+      </x:c>
+      <x:c r="H74" s="30" t="str">
+        <x:v>Included as question-specific context when confirmed and associated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="30" t="str">
+        <x:v>MAP074</x:v>
+      </x:c>
+      <x:c r="B75" s="30" t="str">
+        <x:v>REQ013</x:v>
+      </x:c>
+      <x:c r="C75" s="30" t="str">
+        <x:v>EV010</x:v>
+      </x:c>
+      <x:c r="D75" s="30" t="str">
+        <x:v>Confirmed code-block context</x:v>
+      </x:c>
+      <x:c r="E75" s="30" t="str">
+        <x:v>Conditional</x:v>
+      </x:c>
+      <x:c r="F75" s="30" t="str">
+        <x:v>The question refers to or depends on a code block</x:v>
+      </x:c>
+      <x:c r="G75" s="30" t="str">
+        <x:v>Not Verified</x:v>
+      </x:c>
+      <x:c r="H75" s="30" t="str">
+        <x:v>Included as question-specific context when confirmed and associated.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac5ab72b17824e00"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87802698cfee44b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>